--- a/reports/集团总公司_利润表_2026-12.xlsx
+++ b/reports/集团总公司_利润表_2026-12.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>219388006</v>
+        <v>238641361</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>166995680</v>
+        <v>181208529</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>2054288162</v>
+        <v>2230772145</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>680271</v>
+        <v>878226</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>8475722</v>
+        <v>10974978</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>590548</v>
+        <v>767218</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>7352611</v>
+        <v>9601613</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>498617</v>
+        <v>646949</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>6231026</v>
+        <v>8103348</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>459058</v>
+        <v>596923</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5733542</v>
+        <v>7477840</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>250340</v>
+        <v>328423</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>3115880</v>
+        <v>4111544</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>199903</v>
+        <v>258997</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2492315</v>
+        <v>3238646</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>216709269</v>
+        <v>235164625</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164316943</v>
+        <v>177731793</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84449444</v>
+        <v>92375817</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>1011094547</v>
+        <v>1109984640</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1547596</v>
+        <v>2756719</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>19316516</v>
+        <v>34266491</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1395922</v>
+        <v>2006371</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>17449513</v>
+        <v>24925434</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75253685</v>
+        <v>79331100</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>952209422</v>
+        <v>1002320966</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1602398</v>
+        <v>2004320</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>19937162</v>
+        <v>24942561</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>697156</v>
+        <v>1000186</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>8723505</v>
+        <v>12471920</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2495072</v>
+        <v>2994729</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>31164562</v>
+        <v>37420301</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1102003</v>
+        <v>1496006</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>13709451</v>
+        <v>18706323</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>52219484</v>
+        <v>51983713</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>640624501</v>
+        <v>640435919</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>172842</v>
+        <v>174404</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>2106462</v>
+        <v>2100969</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3163983</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>39626303</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2110732</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>26410387</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>158765331</v>
+        <v>179569510</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>127438375</v>
+        <v>134310101</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>100320274</v>
+        <v>107086916</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1266845337</v>
+        <v>1353544853</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27118101</v>
+        <v>27223185</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>337657192</v>
+        <v>337818614</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5315474</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>66036140</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1701599</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>21137750</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1063121</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>13214902</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1274431</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>15861585</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>954365</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>11897824</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>635129</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>7932021</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>528388</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>6609318</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2936548</v>
+        <v>2936176</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>36762106</v>
+        <v>36774073</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1387411</v>
+        <v>1382730</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>17325927</v>
+        <v>17331041</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3614513</v>
+        <v>3587740</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>44868831</v>
+        <v>44837813</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>23278089</v>
+        <v>23254035</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>300156669</v>
+        <v>300094883</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>353408</v>
+        <v>2854634</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>4346672</v>
+        <v>35492322</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1144398</v>
+        <v>1154317</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>13882534</v>
+        <v>13832809</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1186529</v>
+        <v>1102873</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>14377347</v>
+        <v>13217404</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>121782</v>
+        <v>123933</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1488098</v>
+        <v>1482324</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>493233</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>5894251</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>930558</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>11560167</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>328767</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>3932052</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>246301</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2949764</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>409857</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>4916933</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1322873</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>16524921</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>217849</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>2621986</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163186</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1965997</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>271813</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>3275611</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>190294</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>2292166</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136040</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1636792</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>108985</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>1309191</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81880</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>981838</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>57943938</v>
+        <v>58885253</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>62782100</v>
+        <v>63238759</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>531639</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>6604114</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>137045</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1637907</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>213388</v>
+        <v>217084</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>2603339</v>
+        <v>2596731</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57730550</v>
+        <v>59199808</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7247574</v>
+        <v>7320773</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>88057006</v>
+        <v>87825575</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50482976</v>
+        <v>51879035</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50482976</v>
+        <v>51879035</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50482976</v>
+        <v>51879035</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50482976</v>
+        <v>51879035</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50482976</v>
+        <v>51879035</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
